--- a/employment_forms/020_job_offer_approval_form--employment_forms.xlsx
+++ b/employment_forms/020_job_offer_approval_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'department_a',_'value':_'department_a'}</t>
+          <t>department_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Department A', 'value': 'Department A'}</t>
+          <t>Department A</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'department_b',_'value':_'department_b'}</t>
+          <t>department_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Department B', 'value': 'Department B'}</t>
+          <t>Department B</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'department_c',_'value':_'department_c'}</t>
+          <t>department_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Department C', 'value': 'Department C'}</t>
+          <t>Department C</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full-time', 'value': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Part-time', 'value': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contract',_'value':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Contract', 'value': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'entry_level',_'value':_'entry_level'}</t>
+          <t>entry_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Entry Level', 'value': 'Entry Level'}</t>
+          <t>Entry Level</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mid_level',_'value':_'mid_level'}</t>
+          <t>mid_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Mid Level', 'value': 'Mid Level'}</t>
+          <t>Mid Level</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'senior',_'value':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Senior', 'value': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
